--- a/r4-ELGA-IV-Diabetes-main/StructureDefinition-Datamodel-diab.xlsx
+++ b/r4-ELGA-IV-Diabetes-main/StructureDefinition-Datamodel-diab.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-27T15:05:45+00:00</t>
+    <t>2025-01-30T07:29:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-IV-Diabetes-main/StructureDefinition-Datamodel-diab.xlsx
+++ b/r4-ELGA-IV-Diabetes-main/StructureDefinition-Datamodel-diab.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-30T07:29:10+00:00</t>
+    <t>2025-01-30T08:21:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-IV-Diabetes-main/StructureDefinition-Datamodel-diab.xlsx
+++ b/r4-ELGA-IV-Diabetes-main/StructureDefinition-Datamodel-diab.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://diab.iv.elga.gv.at/StructureDefinition/Datamodel-diab</t>
+    <t>https://fhir.hl7.at/elga-iv-diabetes-r4/StructureDefinition/Datamodel-diab</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-30T08:21:10+00:00</t>
+    <t>2025-02-28T13:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-IV-Diabetes-main/StructureDefinition-Datamodel-diab.xlsx
+++ b/r4-ELGA-IV-Diabetes-main/StructureDefinition-Datamodel-diab.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T13:11:58+00:00</t>
+    <t>2025-02-28T14:02:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-IV-Diabetes-main/StructureDefinition-Datamodel-diab.xlsx
+++ b/r4-ELGA-IV-Diabetes-main/StructureDefinition-Datamodel-diab.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T14:02:02+00:00</t>
+    <t>2025-03-03T10:25:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
